--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MINNESOTA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/MINNESOTA_2019.xlsx
@@ -1842,7 +1842,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C83">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C223">
@@ -8563,7 +8563,7 @@
         <v>60</v>
       </c>
       <c r="D456">
-        <v>0.009312432096849293</v>
+        <v>0.009312432096849291</v>
       </c>
     </row>
     <row r="457">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C634">
